--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Document Reference</t>
+    <t>This StructureDefinition contains the maps for VistA ? (file ?) to FHIR DocumentReference</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA ? (file ?) to FHIR DocumentReference</t>
+    <t>This StructureDefinition contains the maps for VistA TIU DOCUMENT (file 8925) to FHIR DocumentReference</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2538" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2538" uniqueCount="545">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -255,10 +255,10 @@
     <t>Mapping: XDS metadata equivalent</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t/>
@@ -699,10 +699,10 @@
     <t>DocumentEntry.class</t>
   </si>
   <si>
+    <t>875: transform using TIU_VHA_ENTERPRISE_STANDARD_TITLE_8926.1 on TIU DOCUMENT - DOCUMENT TYPE &gt; TIU VHA ENTERPRISE STANDARD TITLE - DOCUMENT TYPE (#8925-.01 &gt; 8926.1-.08)</t>
+  </si>
+  <si>
     <t>Dim.TIUStandardTitle.TIUDocumentTypeIEN</t>
-  </si>
-  <si>
-    <t>875: transform using TIU_VHA_ENTERPRISE_STANDARD_TITLE_8926.1 on TIU DOCUMENT - DOCUMENT TYPE &gt; TIU VHA ENTERPRISE STANDARD TITLE - DOCUMENT TYPE (#8925-.01 &gt; 8926.1-.08)</t>
   </si>
   <si>
     <t>DocumentReference.category:us-core</t>
@@ -786,10 +786,10 @@
     <t>FiveWs.recorded</t>
   </si>
   <si>
+    <t>877: source value from TIU DOCUMENT - ENTRY DATE/TIME (#8925-1201)</t>
+  </si>
+  <si>
     <t>TIU.TIUDocument.EntryDateTime</t>
-  </si>
-  <si>
-    <t>877: source value from TIU DOCUMENT - ENTRY DATE/TIME (#8925-1201)</t>
   </si>
   <si>
     <t>DocumentReference.author</t>
@@ -1034,10 +1034,10 @@
     <t>DocumentEntry.comments</t>
   </si>
   <si>
+    <t>885: source value from TIU DOCUMENT - SUBJECT (#8925-1701)</t>
+  </si>
+  <si>
     <t>TIU.TIUDocument.DocumentSubject</t>
-  </si>
-  <si>
-    <t>885: source value from TIU DOCUMENT - SUBJECT (#8925-1701)</t>
   </si>
   <si>
     <t>DocumentReference.securityLabel</t>
@@ -1181,6 +1181,10 @@
     <t>Attachment.contentType</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-3:889: fixed value "text/plain" {null}</t>
+  </si>
+  <si>
     <t>./mediaType, ./charset</t>
   </si>
   <si>
@@ -1491,10 +1495,10 @@
     <t>DocumentEntry.eventCodeList</t>
   </si>
   <si>
+    <t>900: source value from TIU DOCUMENT - VISIT TYPE (#8925-.13)</t>
+  </si>
+  <si>
     <t>TIU.TIUDocument.VisitType</t>
-  </si>
-  <si>
-    <t>900: source value from TIU DOCUMENT - VISIT TYPE (#8925-.13)</t>
   </si>
   <si>
     <t>DocumentReference.context.period</t>
@@ -1557,12 +1561,12 @@
     <t>DR.1</t>
   </si>
   <si>
+    <t>901: source value from TIU DOCUMENT - EPISODE BEGIN DATE/TIME (#8925-.07)</t>
+  </si>
+  <si>
     <t>TIU.TIUDocument.EpisodeBeginDateTime</t>
   </si>
   <si>
-    <t>901: source value from TIU DOCUMENT - EPISODE BEGIN DATE/TIME (#8925-.07)</t>
-  </si>
-  <si>
     <t>DocumentReference.context.period.end</t>
   </si>
   <si>
@@ -1587,12 +1591,12 @@
     <t>DR.2</t>
   </si>
   <si>
+    <t>902: source value from TIU DOCUMENT - EPISODE END DATE/TIME (#8925-.08)</t>
+  </si>
+  <si>
     <t>TIU.TIUDocument.EpisodeEndDateTime</t>
   </si>
   <si>
-    <t>902: source value from TIU DOCUMENT - EPISODE END DATE/TIME (#8925-.08)</t>
-  </si>
-  <si>
     <t>DocumentReference.context.facilityType</t>
   </si>
   <si>
@@ -1620,10 +1624,10 @@
     <t>DocumentEntry.healthcareFacilityTypeCode</t>
   </si>
   <si>
+    <t>903: source value from TIU DOCUMENT - HOSPITAL LOCATION &gt; HOSPITAL LOCATION - TYPE (#8925-1205 &gt; 44-2)</t>
+  </si>
+  <si>
     <t>Dim.Location.LocationType</t>
-  </si>
-  <si>
-    <t>903: source value from TIU DOCUMENT - HOSPITAL LOCATION &gt; HOSPITAL LOCATION - TYPE (#8925-1205 &gt; 44-2)</t>
   </si>
   <si>
     <t>DocumentReference.context.practiceSetting</t>
@@ -2062,8 +2066,8 @@
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="84.2265625" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="162.44921875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="212.015625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="212.015625" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3489,10 +3493,10 @@
         <v>162</v>
       </c>
       <c r="AR11" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AS11" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3616,10 +3620,10 @@
         <v>169</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AS12" t="s" s="2">
-        <v>170</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" hidden="true">
@@ -4001,10 +4005,10 @@
         <v>204</v>
       </c>
       <c r="AR15" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="AS15" t="s" s="2">
-        <v>205</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" hidden="true">
@@ -4386,10 +4390,10 @@
         <v>236</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>81</v>
+        <v>237</v>
       </c>
       <c r="AS18" t="s" s="2">
-        <v>237</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -4644,10 +4648,10 @@
         <v>260</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="AS20" t="s" s="2">
-        <v>261</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4773,10 +4777,10 @@
         <v>272</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="AS21" t="s" s="2">
-        <v>273</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4902,10 +4906,10 @@
         <v>81</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>81</v>
+        <v>281</v>
       </c>
       <c r="AS22" t="s" s="2">
-        <v>281</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -5936,10 +5940,10 @@
         <v>342</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>81</v>
+        <v>343</v>
       </c>
       <c r="AS30" t="s" s="2">
-        <v>343</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -6190,10 +6194,10 @@
         <v>81</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>81</v>
+        <v>350</v>
       </c>
       <c r="AS32" t="s" s="2">
-        <v>350</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -6704,10 +6708,10 @@
         <v>81</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>81</v>
+        <v>363</v>
       </c>
       <c r="AS36" t="s" s="2">
-        <v>363</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -6938,7 +6942,7 @@
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>105</v>
+        <v>375</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>81</v>
@@ -6947,7 +6951,7 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6956,24 +6960,24 @@
         <v>81</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>81</v>
+        <v>378</v>
       </c>
       <c r="AS38" t="s" s="2">
-        <v>377</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6999,14 +7003,14 @@
         <v>113</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -7019,7 +7023,7 @@
         <v>81</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>81</v>
@@ -7055,7 +7059,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7076,7 +7080,7 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -7091,18 +7095,18 @@
         <v>81</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="AS39" t="s" s="2">
-        <v>385</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7125,19 +7129,19 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -7186,7 +7190,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7195,7 +7199,7 @@
         <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>105</v>
@@ -7207,7 +7211,7 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -7216,24 +7220,24 @@
         <v>81</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>81</v>
+        <v>397</v>
       </c>
       <c r="AS40" t="s" s="2">
-        <v>396</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7256,19 +7260,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -7281,7 +7285,7 @@
         <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>81</v>
@@ -7317,7 +7321,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7326,7 +7330,7 @@
         <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>105</v>
@@ -7338,7 +7342,7 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -7347,7 +7351,7 @@
         <v>81</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>81</v>
@@ -7361,10 +7365,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7387,19 +7391,19 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -7448,7 +7452,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7469,7 +7473,7 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -7484,18 +7488,18 @@
         <v>81</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="AS42" t="s" s="2">
-        <v>415</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7518,19 +7522,19 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7579,7 +7583,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7600,7 +7604,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7615,18 +7619,18 @@
         <v>81</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>81</v>
+        <v>424</v>
       </c>
       <c r="AS43" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7652,14 +7656,14 @@
         <v>291</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7672,7 +7676,7 @@
         <v>81</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>81</v>
@@ -7708,7 +7712,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7729,7 +7733,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -7744,18 +7748,18 @@
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>81</v>
+        <v>432</v>
       </c>
       <c r="AS44" t="s" s="2">
-        <v>431</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7778,17 +7782,17 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7837,7 +7841,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7858,7 +7862,7 @@
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7873,18 +7877,18 @@
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>248</v>
+        <v>439</v>
       </c>
       <c r="AS45" t="s" s="2">
-        <v>438</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7907,16 +7911,16 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7946,7 +7950,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7964,7 +7968,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7982,13 +7986,13 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>348</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7997,21 +8001,21 @@
         <v>81</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8037,13 +8041,13 @@
         <v>283</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8093,7 +8097,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8114,7 +8118,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -8137,10 +8141,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8256,18 +8260,18 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>81</v>
+        <v>456</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>455</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8393,10 +8397,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8524,10 +8528,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8550,13 +8554,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8607,7 +8611,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8622,19 +8626,19 @@
         <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>81</v>
@@ -8643,18 +8647,18 @@
         <v>81</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>81</v>
+        <v>467</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>466</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8680,13 +8684,13 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8715,10 +8719,10 @@
         <v>211</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8736,7 +8740,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8754,10 +8758,10 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -8769,21 +8773,21 @@
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8806,13 +8810,13 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8863,7 +8867,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8881,13 +8885,13 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8896,7 +8900,7 @@
         <v>81</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>81</v>
@@ -8907,10 +8911,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9034,10 +9038,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9163,10 +9167,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9189,16 +9193,16 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9248,7 +9252,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9257,7 +9261,7 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
@@ -9269,7 +9273,7 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
@@ -9278,24 +9282,24 @@
         <v>81</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9318,23 +9322,23 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q57" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="R57" t="s" s="2">
         <v>81</v>
@@ -9379,7 +9383,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9388,7 +9392,7 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>105</v>
@@ -9400,7 +9404,7 @@
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -9409,24 +9413,24 @@
         <v>81</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AS57" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9452,10 +9456,10 @@
         <v>192</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9485,10 +9489,10 @@
         <v>211</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
@@ -9506,7 +9510,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9524,13 +9528,13 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -9539,21 +9543,21 @@
         <v>81</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AS58" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9579,16 +9583,16 @@
         <v>192</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -9616,10 +9620,10 @@
         <v>211</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -9637,7 +9641,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9655,14 +9659,14 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="AN59" t="s" s="2">
-        <v>513</v>
-      </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9670,21 +9674,21 @@
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>81</v>
+        <v>528</v>
       </c>
       <c r="AS59" t="s" s="2">
-        <v>527</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9707,13 +9711,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9764,7 +9768,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9797,21 +9801,21 @@
         <v>81</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>81</v>
+        <v>534</v>
       </c>
       <c r="AS60" t="s" s="2">
-        <v>533</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9834,16 +9838,16 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9893,7 +9897,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9911,13 +9915,13 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>
@@ -9926,13 +9930,13 @@
         <v>81</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>81</v>
+        <v>544</v>
       </c>
       <c r="AS61" t="s" s="2">
-        <v>543</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1182,7 +1182,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-3:889: fixed value "text/plain" {null}</t>
+inv-4:889: fixed value = text/plain {null}</t>
   </si>
   <si>
     <t>./mediaType, ./charset</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA ? (file ?) to FHIR DocumentReference</t>
+    <t>This StructureDefinition contains the maps for VistA file ? (#?) to us-core-documentreference</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
